--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101453</v>
+        <v>101459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101459</v>
+        <v>101461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101461</v>
+        <v>101462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101462</v>
+        <v>101468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101468</v>
+        <v>101472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101472</v>
+        <v>101474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101474</v>
+        <v>101476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101476</v>
+        <v>101489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101489</v>
+        <v>101491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -826,11 +826,7 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kårbacken, Kårbacken, Jmt</t>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101491</v>
+        <v>101494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101506</v>
+        <v>101521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101494</v>
+        <v>101509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101521</v>
+        <v>101522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101509</v>
+        <v>101510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101522</v>
+        <v>101527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101510</v>
+        <v>101515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101527</v>
+        <v>101530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101515</v>
+        <v>101518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101530</v>
+        <v>101536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101518</v>
+        <v>101524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101536</v>
+        <v>101548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101524</v>
+        <v>101536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60818-2025 artfynd.xlsx
+++ b/artfynd/A 60818-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136875207</v>
       </c>
       <c r="B2" t="n">
-        <v>101548</v>
+        <v>101549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136875084</v>
       </c>
       <c r="B3" t="n">
-        <v>101536</v>
+        <v>101537</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
